--- a/registration_forms/019_care_coordination_improvement_session_registration--registration_forms.xlsx
+++ b/registration_forms/019_care_coordination_improvement_session_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'physician_(md/do)',_'value':_'physician'}</t>
+          <t>physician_(md/do)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Physician (MD/DO)', 'value': 'physician'}</t>
+          <t>Physician (MD/DO)</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'nurse_(rn/lpn)',_'value':_'nurse'}</t>
+          <t>nurse_(rn/lpn)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Nurse (RN/LPN)', 'value': 'nurse'}</t>
+          <t>Nurse (RN/LPN)</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'care_manager/coordinator',_'value':_'care_manager'}</t>
+          <t>care_manager/coordinator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Care Manager/Coordinator', 'value': 'care_manager'}</t>
+          <t>Care Manager/Coordinator</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'practice_administrator',_'value':_'administrator'}</t>
+          <t>practice_administrator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Practice Administrator', 'value': 'administrator'}</t>
+          <t>Practice Administrator</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'social_worker',_'value':_'social_worker'}</t>
+          <t>social_worker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Social Worker', 'value': 'social_worker'}</t>
+          <t>Social Worker</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'march_10,_2026_-_10:00_am_(virtual)',_'value':_'session_1'}</t>
+          <t>march_10,_2026_-_10:00_am_(virtual)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'March 10, 2026 - 10:00 AM (Virtual)', 'value': 'session_1'}</t>
+          <t>March 10, 2026 - 10:00 AM (Virtual)</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'march_12,_2026_-_2:00_pm_(in-person)',_'value':_'session_2'}</t>
+          <t>march_12,_2026_-_2:00_pm_(in-person)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'March 12, 2026 - 2:00 PM (In-Person)', 'value': 'session_2'}</t>
+          <t>March 12, 2026 - 2:00 PM (In-Person)</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'march_17,_2026_-_9:00_am_(virtual)',_'value':_'session_3'}</t>
+          <t>march_17,_2026_-_9:00_am_(virtual)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'March 17, 2026 - 9:00 AM (Virtual)', 'value': 'session_3'}</t>
+          <t>March 17, 2026 - 9:00 AM (Virtual)</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'transitions_of_care',_'value':_'transitions'}</t>
+          <t>transitions_of_care</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Transitions of Care', 'value': 'transitions'}</t>
+          <t>Transitions of Care</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'team-based_care_communication',_'value':_'communication'}</t>
+          <t>team-based_care_communication</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Team-Based Care Communication', 'value': 'communication'}</t>
+          <t>Team-Based Care Communication</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'primary_care_provider_(pcp)_engagement',_'value':_'pcp_engagement'}</t>
+          <t>primary_care_provider_(pcp)_engagement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Primary Care Provider (PCP) Engagement', 'value': 'pcp_engagement'}</t>
+          <t>Primary Care Provider (PCP) Engagement</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'patient_education_&amp;_activation',_'value':_'patient_ed'}</t>
+          <t>patient_education_&amp;_activation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Patient Education &amp; Activation', 'value': 'patient_ed'}</t>
+          <t>Patient Education &amp; Activation</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'using_technology_for_coordination',_'value':_'technology'}</t>
+          <t>using_technology_for_coordination</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Using Technology for Coordination', 'value': 'technology'}</t>
+          <t>Using Technology for Coordination</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'lecture_style_(expert_speaker)',_'value':_'lecture'}</t>
+          <t>lecture_style_(expert_speaker)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Lecture Style (Expert Speaker)', 'value': 'lecture'}</t>
+          <t>Lecture Style (Expert Speaker)</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'interactive_group_workshop',_'value':_'interactive'}</t>
+          <t>interactive_group_workshop</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Interactive Group Workshop', 'value': 'interactive'}</t>
+          <t>Interactive Group Workshop</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'case_study_review',_'value':_'case_study'}</t>
+          <t>case_study_review</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Case Study Review', 'value': 'case_study'}</t>
+          <t>Case Study Review</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'open_q&amp;a_session',_'value':_'qa'}</t>
+          <t>open_q&amp;a_session</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Open Q&amp;A Session', 'value': 'qa'}</t>
+          <t>Open Q&amp;A Session</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'registered_and_confirmed',_'value':_'registered'}</t>
+          <t>registered_and_confirmed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Registered and Confirmed', 'value': 'registered'}</t>
+          <t>Registered and Confirmed</t>
         </is>
       </c>
     </row>
